--- a/data/genomics/bacterial/snvphyl/GRiPHin_Summary.xlsx
+++ b/data/genomics/bacterial/snvphyl/GRiPHin_Summary.xlsx
@@ -621,7 +621,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>16-S-119</v>
+        <v>test</v>
       </c>
       <c r="C3" t="str">
         <v>phylo_in_testing</v>
@@ -696,7 +696,7 @@
         <v>assembly</v>
       </c>
       <c r="AC3" t="str">
-        <v>ST81</v>
+        <v>ST00</v>
       </c>
       <c r="AD3" t="str">
         <v>S14Z(91).L35(89).S19(87).L19(94).S12(94).S8(102).L16(111).S7(110)</v>
@@ -734,7 +734,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>1401332-A</v>
+        <v>test2</v>
       </c>
       <c r="C4" t="str">
         <v>phylo_in_testing</v>
@@ -806,7 +806,7 @@
         <v>assembly</v>
       </c>
       <c r="AC4" t="str">
-        <v>ST749</v>
+        <v>ST00</v>
       </c>
       <c r="AD4" t="str">
         <v>dnaA(249).fusA(75).gyrB(265).leuS(249).pyrG(122).rplB(26).rpoB(67)</v>
@@ -877,7 +877,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>1603786-A</v>
+        <v>test3</v>
       </c>
       <c r="C5" t="str">
         <v>phylo_in_testing</v>
@@ -952,7 +952,7 @@
         <v>assembly</v>
       </c>
       <c r="AC5" t="str">
-        <v>ST135</v>
+        <v>ST00</v>
       </c>
       <c r="AD5" t="str">
         <v>dnaA(59).fusA(47).gyrB(59).leuS(9).pyrG(62).rplB(23).rpoB(6)</v>
@@ -1016,235 +1016,6 @@
       </c>
       <c r="BK5" t="str">
         <v>[100NT/100:#16]G</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>1415006a-UT-M03999-190528</v>
-      </c>
-      <c r="C6" t="str">
-        <v>phylo_in_testing</v>
-      </c>
-      <c r="D6" t="str">
-        <v>FAIL</v>
-      </c>
-      <c r="E6" t="str">
-        <v>High scaffold count &gt;500 (1286), assembly stdev &gt;2.58 (15.1385)</v>
-      </c>
-      <c r="F6" t="str">
-        <v>FastANI coverage is &lt;90%</v>
-      </c>
-      <c r="H6" t="str">
-        <v>97.09</v>
-      </c>
-      <c r="I6" t="str">
-        <v>89.51</v>
-      </c>
-      <c r="J6" t="str">
-        <v>1089476</v>
-      </c>
-      <c r="K6" t="str">
-        <v>1029114</v>
-      </c>
-      <c r="L6" t="str">
-        <v>1049117</v>
-      </c>
-      <c r="M6" t="str">
-        <v>30.29</v>
-      </c>
-      <c r="N6" t="str">
-        <v>38.5</v>
-      </c>
-      <c r="O6" t="str">
-        <v>1286</v>
-      </c>
-      <c r="P6" t="str">
-        <v>7696184</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>1.8733</v>
-      </c>
-      <c r="R6" t="str">
-        <v>15.1385</v>
-      </c>
-      <c r="S6" t="str">
-        <v>Acinetobacter seifertii-strain-AS9</v>
-      </c>
-      <c r="T6" t="str">
-        <v>ANI_REFSEQ</v>
-      </c>
-      <c r="U6" t="str">
-        <v>Acinetobacter (94.53) seifertii (50.92).</v>
-      </c>
-      <c r="V6" t="str">
-        <v>Acinetobacter (99.91) seifertii (50.29).</v>
-      </c>
-      <c r="W6" t="str">
-        <v>Acinetobacter seifertii-strain-AS9</v>
-      </c>
-      <c r="X6" t="str">
-        <v>98.21</v>
-      </c>
-      <c r="Y6" t="str">
-        <v>60.24</v>
-      </c>
-      <c r="Z6" t="str">
-        <v>Acinetobacter_seifertii-strain-AS9_GCF_014723155.1_ASM1472315v1_genomic.fna.gz</v>
-      </c>
-      <c r="AA6" t="str">
-        <v>abaumannii(Oxford)</v>
-      </c>
-      <c r="AB6" t="str">
-        <v>assembly</v>
-      </c>
-      <c r="AC6" t="str">
-        <v>ST3212</v>
-      </c>
-      <c r="AD6" t="str">
-        <v>gltA(49).gyrB(308).gdhB(329).recA(53).cpn60(131).gpi(255).rpoD(256)</v>
-      </c>
-      <c r="AE6" t="str">
-        <v>abaumannii(Pasteur)</v>
-      </c>
-      <c r="AF6" t="str">
-        <v>assembly</v>
-      </c>
-      <c r="AG6" t="str">
-        <v>ST544</v>
-      </c>
-      <c r="AH6" t="str">
-        <v>cpn60(83).fusA(86).gltA(34).pyrG(23).recA(88).rplB(23).rpoB(77)</v>
-      </c>
-      <c r="AI6" t="str">
-        <v>ResGANNCBI_20250519([XNT/98AA/90]G:[98NT/90]S)</v>
-      </c>
-      <c r="AO6" t="str">
-        <v>[99NT/98AA/100:#622]G</v>
-      </c>
-      <c r="BF6" t="str">
-        <v>[100NT/100AA/100:#473]G</v>
-      </c>
-      <c r="BG6" t="str">
-        <v>HyperVirulence_20220414</v>
-      </c>
-      <c r="BH6" t="str">
-        <v>[-/-]</v>
-      </c>
-      <c r="BI6" t="str">
-        <v xml:space="preserve">PF-Replicons_20250214([95NT/60]) </v>
-      </c>
-      <c r="BJ6" t="str">
-        <v>[-/-]</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>17314X115_U-PAT-352P_191010_A00421_0119_AHGHJVDRXX</v>
-      </c>
-      <c r="C7" t="str">
-        <v>phylo_in_testing</v>
-      </c>
-      <c r="D7" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="H7" t="str">
-        <v>94.45</v>
-      </c>
-      <c r="I7" t="str">
-        <v>92.19</v>
-      </c>
-      <c r="J7" t="str">
-        <v>2836540</v>
-      </c>
-      <c r="K7" t="str">
-        <v>2610278</v>
-      </c>
-      <c r="L7" t="str">
-        <v>2676423</v>
-      </c>
-      <c r="M7" t="str">
-        <v>84.32</v>
-      </c>
-      <c r="N7" t="str">
-        <v>64.05</v>
-      </c>
-      <c r="O7" t="str">
-        <v>87</v>
-      </c>
-      <c r="P7" t="str">
-        <v>4697350</v>
-      </c>
-      <c r="Q7" t="str">
-        <v>1.0816</v>
-      </c>
-      <c r="R7" t="str">
-        <v>0.6199</v>
-      </c>
-      <c r="S7" t="str">
-        <v>Stutzerimonas stutzeri-DSM-4166</v>
-      </c>
-      <c r="T7" t="str">
-        <v>ANI_REFSEQ</v>
-      </c>
-      <c r="U7" t="str">
-        <v>Stutzerimonas (86.49) stutzeri (66.57).</v>
-      </c>
-      <c r="V7" t="str">
-        <v>Stutzerimonas (97.37) stutzeri (97.26).</v>
-      </c>
-      <c r="W7" t="str">
-        <v>Stutzerimonas stutzeri-DSM-4166</v>
-      </c>
-      <c r="X7" t="str">
-        <v>98.69</v>
-      </c>
-      <c r="Y7" t="str">
-        <v>94.82</v>
-      </c>
-      <c r="Z7" t="str">
-        <v>Stutzerimonas_stutzeri-DSM-4166_GCF_000195105.1_ASM19510v1_genomic.fna.gz</v>
-      </c>
-      <c r="AA7" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB7" t="str">
-        <v>None-Unknown Unknown</v>
-      </c>
-      <c r="AC7" t="str">
-        <v>-</v>
-      </c>
-      <c r="AD7" t="str">
-        <v>-</v>
-      </c>
-      <c r="AE7" t="str">
-        <v>-</v>
-      </c>
-      <c r="AF7" t="str">
-        <v>-</v>
-      </c>
-      <c r="AG7" t="str">
-        <v>-</v>
-      </c>
-      <c r="AH7" t="str">
-        <v>-</v>
-      </c>
-      <c r="AI7" t="str">
-        <v>ResGANNCBI_20250519([XNT/98AA/90]G:[98NT/90]S)</v>
-      </c>
-      <c r="AJ7" t="str">
-        <v>[-/-]</v>
-      </c>
-      <c r="BG7" t="str">
-        <v>HyperVirulence_20220414</v>
-      </c>
-      <c r="BH7" t="str">
-        <v>[-/-]</v>
-      </c>
-      <c r="BI7" t="str">
-        <v xml:space="preserve">PF-Replicons_20250214([95NT/60]) </v>
-      </c>
-      <c r="BJ7" t="str">
-        <v>[-/-]</v>
       </c>
     </row>
     <row r="9">
